--- a/public/documents/pieces-defense/RF-items-classification.xlsx
+++ b/public/documents/pieces-defense/RF-items-classification.xlsx
@@ -477,7 +477,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Items vendus en caisse — un couvert = un plat OU un menu</t>
+          <t>Items vendus en caisse : un couvert = un plat OU un menu</t>
         </is>
       </c>
     </row>
@@ -3611,22 +3611,22 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>Verre ALIGOTE</t>
+          <t>Salade Franc-Comptoi</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>PICHETS :</t>
+          <t>SOLIDE – TVA 10 %</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>boisson</t>
-        </is>
-      </c>
-      <c r="D103" s="4" t="inlineStr">
-        <is>
-          <t>Non</t>
+          <t>plat (salade)</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>Oui</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
@@ -3642,22 +3642,22 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>Salade Franc-Comptoi</t>
+          <t>Verre ALIGOTE</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>SOLIDE – TVA 10 %</t>
+          <t>PICHETS :</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>plat (salade)</t>
-        </is>
-      </c>
-      <c r="D104" s="5" t="inlineStr">
-        <is>
-          <t>Oui</t>
+          <t>boisson</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>Non</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
@@ -4456,7 +4456,7 @@
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>CANCOINE</t>
+          <t>DADOULET</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
@@ -4491,7 +4491,7 @@
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>DADOULET</t>
+          <t>CANCOINE</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
@@ -4790,22 +4790,22 @@
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>Pastis</t>
+          <t>Fondue des Gourmets</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>Autres Apéritifs :</t>
+          <t>SOLIDE – TVA 10 %</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>boisson</t>
-        </is>
-      </c>
-      <c r="D140" s="4" t="inlineStr">
-        <is>
-          <t>Non</t>
+          <t>plat</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr">
+        <is>
+          <t>Oui</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
@@ -4821,22 +4821,22 @@
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>Fondue des Gourmets</t>
+          <t>Pastis</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>SOLIDE – TVA 10 %</t>
+          <t>Autres Apéritifs :</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>plat</t>
-        </is>
-      </c>
-      <c r="D141" s="5" t="inlineStr">
-        <is>
-          <t>Oui</t>
+          <t>boisson</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>Non</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
@@ -6442,17 +6442,17 @@
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>BAGATELLE</t>
+          <t>PICHET SAINT VERAN</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>SOLIDE – TVA 10 %</t>
+          <t>Vins Blancs :</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>dessert</t>
+          <t>boisson</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr">
@@ -6460,16 +6460,12 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="E192" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="F192" s="6" t="inlineStr">
-        <is>
-          <t>nom de crêpe/coupe sucrée : à confirmer sur la carte</t>
-        </is>
-      </c>
+      <c r="E192" s="4" t="inlineStr">
+        <is>
+          <t>haute</t>
+        </is>
+      </c>
+      <c r="F192" s="6" t="inlineStr"/>
       <c r="G192" s="4" t="n">
         <v>110</v>
       </c>
@@ -6477,17 +6473,17 @@
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>PICHET SAINT VERAN</t>
+          <t>BAGATELLE</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Vins Blancs :</t>
+          <t>SOLIDE – TVA 10 %</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>boisson</t>
+          <t>dessert</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
@@ -6495,12 +6491,16 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="E193" s="4" t="inlineStr">
-        <is>
-          <t>haute</t>
-        </is>
-      </c>
-      <c r="F193" s="6" t="inlineStr"/>
+      <c r="E193" s="7" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="F193" s="6" t="inlineStr">
+        <is>
+          <t>nom de crêpe/coupe sucrée : à confirmer sur la carte</t>
+        </is>
+      </c>
       <c r="G193" s="4" t="n">
         <v>110</v>
       </c>
@@ -6772,17 +6772,17 @@
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
         <is>
-          <t>Sauce Morilles</t>
+          <t>PICHET MOULIN A VENT</t>
         </is>
       </c>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>SOLIDE – TVA 10 %</t>
+          <t>Vins Rouges :</t>
         </is>
       </c>
       <c r="C202" s="4" t="inlineStr">
         <is>
-          <t>dessert</t>
+          <t>boisson</t>
         </is>
       </c>
       <c r="D202" s="4" t="inlineStr">
@@ -6803,17 +6803,17 @@
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>PICHET MOULIN A VENT</t>
+          <t>Sauce Morilles</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Vins Rouges :</t>
+          <t>SOLIDE – TVA 10 %</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>boisson</t>
+          <t>dessert</t>
         </is>
       </c>
       <c r="D203" s="4" t="inlineStr">
@@ -7055,17 +7055,17 @@
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>Mi</t>
+          <t>CONQUÊTE</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>AUTRES :</t>
+          <t>SOLIDE – TVA 10 %</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>boisson</t>
+          <t>dessert</t>
         </is>
       </c>
       <c r="D211" s="4" t="inlineStr">
@@ -7073,12 +7073,16 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="E211" s="4" t="inlineStr">
-        <is>
-          <t>haute</t>
-        </is>
-      </c>
-      <c r="F211" s="6" t="inlineStr"/>
+      <c r="E211" s="7" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="F211" s="6" t="inlineStr">
+        <is>
+          <t>nom de crêpe/coupe sucrée : à confirmer sur la carte</t>
+        </is>
+      </c>
       <c r="G211" s="4" t="n">
         <v>86</v>
       </c>
@@ -7086,17 +7090,17 @@
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
         <is>
-          <t>CONQUÊTE</t>
+          <t>Mi</t>
         </is>
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>SOLIDE – TVA 10 %</t>
+          <t>AUTRES :</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>dessert</t>
+          <t>boisson</t>
         </is>
       </c>
       <c r="D212" s="4" t="inlineStr">
@@ -7104,16 +7108,12 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="E212" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="F212" s="6" t="inlineStr">
-        <is>
-          <t>nom de crêpe/coupe sucrée : à confirmer sur la carte</t>
-        </is>
-      </c>
+      <c r="E212" s="4" t="inlineStr">
+        <is>
+          <t>haute</t>
+        </is>
+      </c>
+      <c r="F212" s="6" t="inlineStr"/>
       <c r="G212" s="4" t="n">
         <v>86</v>
       </c>
@@ -7152,7 +7152,7 @@
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
         <is>
-          <t>TOQUADE</t>
+          <t>BASILIC</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
@@ -7187,12 +7187,12 @@
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>Get 27 (4cl)</t>
+          <t>H.C.B BEAUNE BTL</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>Digestifs :</t>
+          <t>Vins Rouges :</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
@@ -7218,17 +7218,17 @@
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>H.C.B BEAUNE BTL</t>
+          <t>TOQUADE</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>Vins Rouges :</t>
+          <t>SOLIDE – TVA 10 %</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>boisson</t>
+          <t>dessert</t>
         </is>
       </c>
       <c r="D216" s="4" t="inlineStr">
@@ -7236,12 +7236,16 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="E216" s="4" t="inlineStr">
-        <is>
-          <t>haute</t>
-        </is>
-      </c>
-      <c r="F216" s="6" t="inlineStr"/>
+      <c r="E216" s="7" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="F216" s="6" t="inlineStr">
+        <is>
+          <t>nom de crêpe/coupe sucrée : à confirmer sur la carte</t>
+        </is>
+      </c>
       <c r="G216" s="4" t="n">
         <v>83</v>
       </c>
@@ -7249,17 +7253,17 @@
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>BASILIC</t>
+          <t>Get 27 (4cl)</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>SOLIDE – TVA 10 %</t>
+          <t>Digestifs :</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>dessert</t>
+          <t>boisson</t>
         </is>
       </c>
       <c r="D217" s="4" t="inlineStr">
@@ -7267,16 +7271,12 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="E217" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="F217" s="6" t="inlineStr">
-        <is>
-          <t>nom de crêpe/coupe sucrée : à confirmer sur la carte</t>
-        </is>
-      </c>
+      <c r="E217" s="4" t="inlineStr">
+        <is>
+          <t>haute</t>
+        </is>
+      </c>
+      <c r="F217" s="6" t="inlineStr"/>
       <c r="G217" s="4" t="n">
         <v>83</v>
       </c>
@@ -7990,17 +7990,17 @@
     <row r="240">
       <c r="A240" s="4" t="inlineStr">
         <is>
-          <t>Jus de citron</t>
+          <t>PICHET HCB</t>
         </is>
       </c>
       <c r="B240" s="4" t="inlineStr">
         <is>
-          <t>SOLIDE – TVA 10 %</t>
+          <t>Vins Rouges :</t>
         </is>
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>accompagnement</t>
+          <t>boisson</t>
         </is>
       </c>
       <c r="D240" s="4" t="inlineStr">
@@ -8021,17 +8021,17 @@
     <row r="241">
       <c r="A241" s="4" t="inlineStr">
         <is>
-          <t>PICHET HCB</t>
+          <t>Jus de citron</t>
         </is>
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>Vins Rouges :</t>
+          <t>SOLIDE – TVA 10 %</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>boisson</t>
+          <t>accompagnement</t>
         </is>
       </c>
       <c r="D241" s="4" t="inlineStr">
@@ -8145,17 +8145,17 @@
     <row r="245">
       <c r="A245" s="4" t="inlineStr">
         <is>
-          <t>CALIN</t>
+          <t>Rabasse</t>
         </is>
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>SOLIDE – TVA 10 %</t>
+          <t>COCKTAÏLS :</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>dessert</t>
+          <t>boisson</t>
         </is>
       </c>
       <c r="D245" s="4" t="inlineStr">
@@ -8163,16 +8163,12 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="E245" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="F245" s="6" t="inlineStr">
-        <is>
-          <t>nom de crêpe/coupe sucrée : à confirmer sur la carte</t>
-        </is>
-      </c>
+      <c r="E245" s="4" t="inlineStr">
+        <is>
+          <t>haute</t>
+        </is>
+      </c>
+      <c r="F245" s="6" t="inlineStr"/>
       <c r="G245" s="4" t="n">
         <v>52</v>
       </c>
@@ -8180,17 +8176,17 @@
     <row r="246">
       <c r="A246" s="4" t="inlineStr">
         <is>
-          <t>Rabasse</t>
+          <t>CALIN</t>
         </is>
       </c>
       <c r="B246" s="4" t="inlineStr">
         <is>
-          <t>COCKTAÏLS :</t>
+          <t>SOLIDE – TVA 10 %</t>
         </is>
       </c>
       <c r="C246" s="4" t="inlineStr">
         <is>
-          <t>boisson</t>
+          <t>dessert</t>
         </is>
       </c>
       <c r="D246" s="4" t="inlineStr">
@@ -8198,12 +8194,16 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="E246" s="4" t="inlineStr">
-        <is>
-          <t>haute</t>
-        </is>
-      </c>
-      <c r="F246" s="6" t="inlineStr"/>
+      <c r="E246" s="7" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="F246" s="6" t="inlineStr">
+        <is>
+          <t>nom de crêpe/coupe sucrée : à confirmer sur la carte</t>
+        </is>
+      </c>
       <c r="G246" s="4" t="n">
         <v>52</v>
       </c>
@@ -8494,17 +8494,17 @@
     <row r="256">
       <c r="A256" s="4" t="inlineStr">
         <is>
-          <t>VERRE H.C.DE BEAUNE</t>
+          <t>COULIS FRAMBOISE</t>
         </is>
       </c>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>Vins Rouges :</t>
+          <t>SOLIDE – TVA 10 %</t>
         </is>
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>boisson</t>
+          <t>dessert</t>
         </is>
       </c>
       <c r="D256" s="4" t="inlineStr">
@@ -8525,17 +8525,17 @@
     <row r="257">
       <c r="A257" s="4" t="inlineStr">
         <is>
-          <t>COULIS FRAMBOISE</t>
+          <t>VERRE H.C.DE BEAUNE</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>SOLIDE – TVA 10 %</t>
+          <t>Vins Rouges :</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>dessert</t>
+          <t>boisson</t>
         </is>
       </c>
       <c r="D257" s="4" t="inlineStr">
@@ -8711,17 +8711,17 @@
     <row r="263">
       <c r="A263" s="4" t="inlineStr">
         <is>
-          <t>Coupe glacée</t>
+          <t>Alsace Gewurztramine</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>SOLIDE – TVA 10 %</t>
+          <t>Vins Blancs :</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>dessert</t>
+          <t>boisson</t>
         </is>
       </c>
       <c r="D263" s="4" t="inlineStr">
@@ -8742,17 +8742,17 @@
     <row r="264">
       <c r="A264" s="4" t="inlineStr">
         <is>
-          <t>Alsace Gewurztramine</t>
+          <t>Coupe glacée</t>
         </is>
       </c>
       <c r="B264" s="4" t="inlineStr">
         <is>
-          <t>Vins Blancs :</t>
+          <t>SOLIDE – TVA 10 %</t>
         </is>
       </c>
       <c r="C264" s="4" t="inlineStr">
         <is>
-          <t>boisson</t>
+          <t>dessert</t>
         </is>
       </c>
       <c r="D264" s="4" t="inlineStr">
@@ -9052,7 +9052,7 @@
     <row r="274">
       <c r="A274" s="4" t="inlineStr">
         <is>
-          <t>Flambée</t>
+          <t>CREPE CHOC/CHANTILLY</t>
         </is>
       </c>
       <c r="B274" s="4" t="inlineStr">
@@ -9083,17 +9083,17 @@
     <row r="275">
       <c r="A275" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>IVRESSE</t>
         </is>
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>AUTRES :</t>
+          <t>SOLIDE – TVA 10 %</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>boisson</t>
+          <t>dessert</t>
         </is>
       </c>
       <c r="D275" s="4" t="inlineStr">
@@ -9101,12 +9101,16 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="E275" s="4" t="inlineStr">
-        <is>
-          <t>haute</t>
-        </is>
-      </c>
-      <c r="F275" s="6" t="inlineStr"/>
+      <c r="E275" s="7" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="F275" s="6" t="inlineStr">
+        <is>
+          <t>nom de crêpe/coupe sucrée : à confirmer sur la carte</t>
+        </is>
+      </c>
       <c r="G275" s="4" t="n">
         <v>23</v>
       </c>
@@ -9114,17 +9118,17 @@
     <row r="276">
       <c r="A276" s="4" t="inlineStr">
         <is>
-          <t>CREPE CHOC/CHANTILLY</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="B276" s="4" t="inlineStr">
         <is>
-          <t>SOLIDE – TVA 10 %</t>
+          <t>AUTRES :</t>
         </is>
       </c>
       <c r="C276" s="4" t="inlineStr">
         <is>
-          <t>dessert</t>
+          <t>boisson</t>
         </is>
       </c>
       <c r="D276" s="4" t="inlineStr">
@@ -9145,17 +9149,17 @@
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
         <is>
-          <t>Cognac (4cl)</t>
+          <t>Flambée</t>
         </is>
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>Digestifs :</t>
+          <t>SOLIDE – TVA 10 %</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>boisson</t>
+          <t>dessert</t>
         </is>
       </c>
       <c r="D277" s="4" t="inlineStr">
@@ -9176,17 +9180,17 @@
     <row r="278">
       <c r="A278" s="4" t="inlineStr">
         <is>
-          <t>IVRESSE</t>
+          <t>Cognac (4cl)</t>
         </is>
       </c>
       <c r="B278" s="4" t="inlineStr">
         <is>
-          <t>SOLIDE – TVA 10 %</t>
+          <t>Digestifs :</t>
         </is>
       </c>
       <c r="C278" s="4" t="inlineStr">
         <is>
-          <t>dessert</t>
+          <t>boisson</t>
         </is>
       </c>
       <c r="D278" s="4" t="inlineStr">
@@ -9194,16 +9198,12 @@
           <t>Non</t>
         </is>
       </c>
-      <c r="E278" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="F278" s="6" t="inlineStr">
-        <is>
-          <t>nom de crêpe/coupe sucrée : à confirmer sur la carte</t>
-        </is>
-      </c>
+      <c r="E278" s="4" t="inlineStr">
+        <is>
+          <t>haute</t>
+        </is>
+      </c>
+      <c r="F278" s="6" t="inlineStr"/>
       <c r="G278" s="4" t="n">
         <v>23</v>
       </c>
@@ -9463,17 +9463,17 @@
     <row r="287">
       <c r="A287" s="4" t="inlineStr">
         <is>
-          <t>Crément du Jura</t>
+          <t>Miel</t>
         </is>
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>Pétillants :</t>
+          <t>SOLIDE – TVA 10 %</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>boisson</t>
+          <t>dessert</t>
         </is>
       </c>
       <c r="D287" s="4" t="inlineStr">
@@ -9494,7 +9494,7 @@
     <row r="288">
       <c r="A288" s="4" t="inlineStr">
         <is>
-          <t>Miel</t>
+          <t>Beurre</t>
         </is>
       </c>
       <c r="B288" s="4" t="inlineStr">
@@ -9504,7 +9504,7 @@
       </c>
       <c r="C288" s="4" t="inlineStr">
         <is>
-          <t>dessert</t>
+          <t>accompagnement</t>
         </is>
       </c>
       <c r="D288" s="4" t="inlineStr">
@@ -9525,17 +9525,17 @@
     <row r="289">
       <c r="A289" s="4" t="inlineStr">
         <is>
-          <t>Beurre</t>
+          <t>Crément du Jura</t>
         </is>
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>SOLIDE – TVA 10 %</t>
+          <t>Pétillants :</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>accompagnement</t>
+          <t>boisson</t>
         </is>
       </c>
       <c r="D289" s="4" t="inlineStr">
@@ -9556,30 +9556,34 @@
     <row r="290">
       <c r="A290" s="4" t="inlineStr">
         <is>
-          <t>GASCOGNE Gd PAVOIS</t>
+          <t>GALETTE FORESTIERE</t>
         </is>
       </c>
       <c r="B290" s="4" t="inlineStr">
         <is>
-          <t>Vins Blancs :</t>
+          <t>SOLIDE – TVA 10 %</t>
         </is>
       </c>
       <c r="C290" s="4" t="inlineStr">
         <is>
-          <t>boisson</t>
-        </is>
-      </c>
-      <c r="D290" s="4" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="E290" s="4" t="inlineStr">
-        <is>
-          <t>haute</t>
-        </is>
-      </c>
-      <c r="F290" s="6" t="inlineStr"/>
+          <t>plat (galette)</t>
+        </is>
+      </c>
+      <c r="D290" s="5" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="E290" s="7" t="inlineStr">
+        <is>
+          <t>à vérifier</t>
+        </is>
+      </c>
+      <c r="F290" s="6" t="inlineStr">
+        <is>
+          <t>nom de galette : à confirmer sur la carte</t>
+        </is>
+      </c>
       <c r="G290" s="4" t="n">
         <v>13</v>
       </c>
@@ -9587,34 +9591,30 @@
     <row r="291">
       <c r="A291" s="4" t="inlineStr">
         <is>
-          <t>GALETTE FORESTIERE</t>
+          <t>GASCOGNE Gd PAVOIS</t>
         </is>
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>SOLIDE – TVA 10 %</t>
+          <t>Vins Blancs :</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>plat (galette)</t>
-        </is>
-      </c>
-      <c r="D291" s="5" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="E291" s="7" t="inlineStr">
-        <is>
-          <t>à vérifier</t>
-        </is>
-      </c>
-      <c r="F291" s="6" t="inlineStr">
-        <is>
-          <t>nom de galette : à confirmer sur la carte</t>
-        </is>
-      </c>
+          <t>boisson</t>
+        </is>
+      </c>
+      <c r="D291" s="4" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="E291" s="4" t="inlineStr">
+        <is>
+          <t>haute</t>
+        </is>
+      </c>
+      <c r="F291" s="6" t="inlineStr"/>
       <c r="G291" s="4" t="n">
         <v>13</v>
       </c>
@@ -9653,7 +9653,7 @@
     <row r="293">
       <c r="A293" s="4" t="inlineStr">
         <is>
-          <t>Crepe NUTELLA/B</t>
+          <t>Caramel</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
@@ -9684,17 +9684,17 @@
     <row r="294">
       <c r="A294" s="4" t="inlineStr">
         <is>
-          <t>Caramel</t>
+          <t>Double Expresso Crèm</t>
         </is>
       </c>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>SOLIDE – TVA 10 %</t>
+          <t>LIQUIDE – TVA 10 %</t>
         </is>
       </c>
       <c r="C294" s="4" t="inlineStr">
         <is>
-          <t>dessert</t>
+          <t>boisson</t>
         </is>
       </c>
       <c r="D294" s="4" t="inlineStr">
@@ -9715,17 +9715,17 @@
     <row r="295">
       <c r="A295" s="4" t="inlineStr">
         <is>
-          <t>Double Expresso Crèm</t>
+          <t>Crepe NUTELLA/B</t>
         </is>
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>LIQUIDE – TVA 10 %</t>
+          <t>SOLIDE – TVA 10 %</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>boisson</t>
+          <t>dessert</t>
         </is>
       </c>
       <c r="D295" s="4" t="inlineStr">
@@ -9843,17 +9843,17 @@
     <row r="299">
       <c r="A299" s="4" t="inlineStr">
         <is>
-          <t>BORD.  MOUTON CADET</t>
+          <t>Crême de marrons</t>
         </is>
       </c>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>Vins Rouges :</t>
+          <t>SOLIDE – TVA 10 %</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>boisson</t>
+          <t>dessert</t>
         </is>
       </c>
       <c r="D299" s="4" t="inlineStr">
@@ -9874,17 +9874,17 @@
     <row r="300">
       <c r="A300" s="4" t="inlineStr">
         <is>
-          <t>Confiture</t>
+          <t>PICHET C.DE BEAUNE B</t>
         </is>
       </c>
       <c r="B300" s="4" t="inlineStr">
         <is>
-          <t>SOLIDE – TVA 10 %</t>
+          <t>Vins Blancs :</t>
         </is>
       </c>
       <c r="C300" s="4" t="inlineStr">
         <is>
-          <t>dessert</t>
+          <t>boisson</t>
         </is>
       </c>
       <c r="D300" s="4" t="inlineStr">
@@ -9905,17 +9905,17 @@
     <row r="301">
       <c r="A301" s="4" t="inlineStr">
         <is>
-          <t>Crême de marrons</t>
+          <t>BORD.  MOUTON CADET</t>
         </is>
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>SOLIDE – TVA 10 %</t>
+          <t>Vins Rouges :</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>dessert</t>
+          <t>boisson</t>
         </is>
       </c>
       <c r="D301" s="4" t="inlineStr">
@@ -9936,17 +9936,17 @@
     <row r="302">
       <c r="A302" s="4" t="inlineStr">
         <is>
-          <t>PICHET C.DE BEAUNE B</t>
+          <t>Confiture</t>
         </is>
       </c>
       <c r="B302" s="4" t="inlineStr">
         <is>
-          <t>Vins Blancs :</t>
+          <t>SOLIDE – TVA 10 %</t>
         </is>
       </c>
       <c r="C302" s="4" t="inlineStr">
         <is>
-          <t>boisson</t>
+          <t>dessert</t>
         </is>
       </c>
       <c r="D302" s="4" t="inlineStr">
@@ -9998,12 +9998,12 @@
     <row r="304">
       <c r="A304" s="4" t="inlineStr">
         <is>
-          <t>H.C.BEAUNE BOUTEILLE</t>
+          <t>MIRAVAL</t>
         </is>
       </c>
       <c r="B304" s="4" t="inlineStr">
         <is>
-          <t>Vins Rouges :</t>
+          <t>Vins Rosés :</t>
         </is>
       </c>
       <c r="C304" s="4" t="inlineStr">
@@ -10029,12 +10029,12 @@
     <row r="305">
       <c r="A305" s="4" t="inlineStr">
         <is>
-          <t>MIRAVAL</t>
+          <t>H.C.BEAUNE BOUTEILLE</t>
         </is>
       </c>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>Vins Rosés :</t>
+          <t>Vins Rouges :</t>
         </is>
       </c>
       <c r="C305" s="4" t="inlineStr">
@@ -10060,17 +10060,17 @@
     <row r="306">
       <c r="A306" s="4" t="inlineStr">
         <is>
-          <t>Crepe CHOCO/BANANE</t>
+          <t>Kir Pamplemousse</t>
         </is>
       </c>
       <c r="B306" s="4" t="inlineStr">
         <is>
-          <t>SOLIDE – TVA 10 %</t>
+          <t>Autres Apéritifs :</t>
         </is>
       </c>
       <c r="C306" s="4" t="inlineStr">
         <is>
-          <t>dessert</t>
+          <t>boisson</t>
         </is>
       </c>
       <c r="D306" s="4" t="inlineStr">
@@ -10091,17 +10091,17 @@
     <row r="307">
       <c r="A307" s="4" t="inlineStr">
         <is>
-          <t>Kir Pamplemousse</t>
+          <t>Crepe CHOCO/BANANE</t>
         </is>
       </c>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>Autres Apéritifs :</t>
+          <t>SOLIDE – TVA 10 %</t>
         </is>
       </c>
       <c r="C307" s="4" t="inlineStr">
         <is>
-          <t>boisson</t>
+          <t>dessert</t>
         </is>
       </c>
       <c r="D307" s="4" t="inlineStr">
@@ -10153,17 +10153,17 @@
     <row r="309">
       <c r="A309" s="4" t="inlineStr">
         <is>
-          <t>Oignons</t>
+          <t>Vieux Marc Bourgogne</t>
         </is>
       </c>
       <c r="B309" s="4" t="inlineStr">
         <is>
-          <t>SOLIDE – TVA 10 %</t>
+          <t>Digestifs :</t>
         </is>
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>accompagnement</t>
+          <t>boisson</t>
         </is>
       </c>
       <c r="D309" s="4" t="inlineStr">
@@ -10184,17 +10184,17 @@
     <row r="310">
       <c r="A310" s="4" t="inlineStr">
         <is>
-          <t>Vieux Marc Bourgogne</t>
+          <t>Oignons</t>
         </is>
       </c>
       <c r="B310" s="4" t="inlineStr">
         <is>
-          <t>Digestifs :</t>
+          <t>SOLIDE – TVA 10 %</t>
         </is>
       </c>
       <c r="C310" s="4" t="inlineStr">
         <is>
-          <t>boisson</t>
+          <t>accompagnement</t>
         </is>
       </c>
       <c r="D310" s="4" t="inlineStr">
@@ -10246,12 +10246,12 @@
     <row r="312">
       <c r="A312" s="4" t="inlineStr">
         <is>
-          <t>Calvados</t>
+          <t>Crément / Jura VERRE</t>
         </is>
       </c>
       <c r="B312" s="4" t="inlineStr">
         <is>
-          <t>Digestifs :</t>
+          <t>Pétillants :</t>
         </is>
       </c>
       <c r="C312" s="4" t="inlineStr">
@@ -10277,12 +10277,12 @@
     <row r="313">
       <c r="A313" s="4" t="inlineStr">
         <is>
-          <t>"Champagne Brut "</t>
+          <t>Calvados</t>
         </is>
       </c>
       <c r="B313" s="4" t="inlineStr">
         <is>
-          <t>Pétillants :</t>
+          <t>Digestifs :</t>
         </is>
       </c>
       <c r="C313" s="4" t="inlineStr">
@@ -10308,7 +10308,7 @@
     <row r="314">
       <c r="A314" s="4" t="inlineStr">
         <is>
-          <t>Crément / Jura VERRE</t>
+          <t>"Champagne Brut "</t>
         </is>
       </c>
       <c r="B314" s="4" t="inlineStr">
@@ -10339,17 +10339,17 @@
     <row r="315">
       <c r="A315" s="4" t="inlineStr">
         <is>
-          <t>H.COTES DE NUITS</t>
+          <t>CREPE MARRON CHANTIL</t>
         </is>
       </c>
       <c r="B315" s="4" t="inlineStr">
         <is>
-          <t>Vins Blancs :</t>
+          <t>SOLIDE – TVA 10 %</t>
         </is>
       </c>
       <c r="C315" s="4" t="inlineStr">
         <is>
-          <t>boisson</t>
+          <t>dessert</t>
         </is>
       </c>
       <c r="D315" s="4" t="inlineStr">
@@ -10370,7 +10370,7 @@
     <row r="316">
       <c r="A316" s="4" t="inlineStr">
         <is>
-          <t>CREPE MARRON CHANTIL</t>
+          <t>Churros</t>
         </is>
       </c>
       <c r="B316" s="4" t="inlineStr">
@@ -10401,7 +10401,7 @@
     <row r="317">
       <c r="A317" s="4" t="inlineStr">
         <is>
-          <t>Churros</t>
+          <t>Tomates</t>
         </is>
       </c>
       <c r="B317" s="4" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="C317" s="4" t="inlineStr">
         <is>
-          <t>dessert</t>
+          <t>accompagnement</t>
         </is>
       </c>
       <c r="D317" s="4" t="inlineStr">
@@ -10432,17 +10432,17 @@
     <row r="318">
       <c r="A318" s="4" t="inlineStr">
         <is>
-          <t>Tomates</t>
+          <t>H.COTES DE NUITS</t>
         </is>
       </c>
       <c r="B318" s="4" t="inlineStr">
         <is>
-          <t>SOLIDE – TVA 10 %</t>
+          <t>Vins Blancs :</t>
         </is>
       </c>
       <c r="C318" s="4" t="inlineStr">
         <is>
-          <t>accompagnement</t>
+          <t>boisson</t>
         </is>
       </c>
       <c r="D318" s="4" t="inlineStr">
@@ -10463,7 +10463,7 @@
     <row r="319">
       <c r="A319" s="4" t="inlineStr">
         <is>
-          <t>Gigot d'Agneau</t>
+          <t>CRUMBLE</t>
         </is>
       </c>
       <c r="B319" s="4" t="inlineStr">
@@ -10473,12 +10473,12 @@
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>plat</t>
-        </is>
-      </c>
-      <c r="D319" s="5" t="inlineStr">
-        <is>
-          <t>Oui</t>
+          <t>dessert</t>
+        </is>
+      </c>
+      <c r="D319" s="4" t="inlineStr">
+        <is>
+          <t>Non</t>
         </is>
       </c>
       <c r="E319" s="4" t="inlineStr">
@@ -10494,7 +10494,7 @@
     <row r="320">
       <c r="A320" s="4" t="inlineStr">
         <is>
-          <t>Bleu de Gex</t>
+          <t>CREPE CHOC/POIRE</t>
         </is>
       </c>
       <c r="B320" s="4" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="C320" s="4" t="inlineStr">
         <is>
-          <t>accompagnement</t>
+          <t>dessert</t>
         </is>
       </c>
       <c r="D320" s="4" t="inlineStr">
@@ -10525,7 +10525,7 @@
     <row r="321">
       <c r="A321" s="4" t="inlineStr">
         <is>
-          <t>CRUMBLE</t>
+          <t>Gigot d'Agneau</t>
         </is>
       </c>
       <c r="B321" s="4" t="inlineStr">
@@ -10535,12 +10535,12 @@
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>dessert</t>
-        </is>
-      </c>
-      <c r="D321" s="4" t="inlineStr">
-        <is>
-          <t>Non</t>
+          <t>plat</t>
+        </is>
+      </c>
+      <c r="D321" s="5" t="inlineStr">
+        <is>
+          <t>Oui</t>
         </is>
       </c>
       <c r="E321" s="4" t="inlineStr">
@@ -10556,7 +10556,7 @@
     <row r="322">
       <c r="A322" s="4" t="inlineStr">
         <is>
-          <t>CREPE CHOC/POIRE</t>
+          <t>Bleu de Gex</t>
         </is>
       </c>
       <c r="B322" s="4" t="inlineStr">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C322" s="4" t="inlineStr">
         <is>
-          <t>dessert</t>
+          <t>accompagnement</t>
         </is>
       </c>
       <c r="D322" s="4" t="inlineStr">
@@ -10587,17 +10587,17 @@
     <row r="323">
       <c r="A323" s="4" t="inlineStr">
         <is>
-          <t>Dessert du jour</t>
+          <t>Guignolet</t>
         </is>
       </c>
       <c r="B323" s="4" t="inlineStr">
         <is>
-          <t>SOLIDE – TVA 10 %</t>
+          <t>AUTRES :</t>
         </is>
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>dessert</t>
+          <t>boisson</t>
         </is>
       </c>
       <c r="D323" s="4" t="inlineStr">
@@ -10618,17 +10618,17 @@
     <row r="324">
       <c r="A324" s="4" t="inlineStr">
         <is>
-          <t>Crémant Rosé</t>
+          <t>Dessert du jour</t>
         </is>
       </c>
       <c r="B324" s="4" t="inlineStr">
         <is>
-          <t>Pétillants :</t>
+          <t>SOLIDE – TVA 10 %</t>
         </is>
       </c>
       <c r="C324" s="4" t="inlineStr">
         <is>
-          <t>boisson</t>
+          <t>dessert</t>
         </is>
       </c>
       <c r="D324" s="4" t="inlineStr">
@@ -10649,17 +10649,17 @@
     <row r="325">
       <c r="A325" s="4" t="inlineStr">
         <is>
-          <t>Guignolet</t>
+          <t>Griottines</t>
         </is>
       </c>
       <c r="B325" s="4" t="inlineStr">
         <is>
-          <t>AUTRES :</t>
+          <t>SOLIDE – TVA 10 %</t>
         </is>
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
-          <t>boisson</t>
+          <t>dessert</t>
         </is>
       </c>
       <c r="D325" s="4" t="inlineStr">
@@ -10680,17 +10680,17 @@
     <row r="326">
       <c r="A326" s="4" t="inlineStr">
         <is>
-          <t>Griottines</t>
+          <t>TEQUILA</t>
         </is>
       </c>
       <c r="B326" s="4" t="inlineStr">
         <is>
-          <t>SOLIDE – TVA 10 %</t>
+          <t>Digestifs :</t>
         </is>
       </c>
       <c r="C326" s="4" t="inlineStr">
         <is>
-          <t>dessert</t>
+          <t>boisson</t>
         </is>
       </c>
       <c r="D326" s="4" t="inlineStr">
@@ -10711,12 +10711,12 @@
     <row r="327">
       <c r="A327" s="4" t="inlineStr">
         <is>
-          <t>TEQUILA</t>
+          <t>Crémant Rosé</t>
         </is>
       </c>
       <c r="B327" s="4" t="inlineStr">
         <is>
-          <t>Digestifs :</t>
+          <t>Pétillants :</t>
         </is>
       </c>
       <c r="C327" s="4" t="inlineStr">
